--- a/光伏配储项目/电价数据/2026/光孝站.xlsx
+++ b/光伏配储项目/电价数据/2026/光孝站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51159</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76313</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57485</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60438</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5209199999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.51924</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45447</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44462</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42266</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4090299999999999</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39859</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38498</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42077</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4239</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41334</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.13099</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12208</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.11182</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13485</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0502</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11219</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.16455</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.09159</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05403</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.10361</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.04090999999999999</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15348</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21721</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26177</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24598</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.12296</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.00859</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14459</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.21637</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.66246</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55974</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.58477</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.38145</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.62905</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44752</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.44403</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.58129</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.48152</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6445599999999999</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.82929</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.65838</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.8108300000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.21557</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43283</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6938799999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60297</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.8519</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.65973</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.67062</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.65695</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6275700000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48073</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41619</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42587</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71254</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.77291</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7973899999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.53334</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8556699999999999</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51837</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5050899999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51058</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48805</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40294</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4696</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38116</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37467</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.49883</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6006</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.74386</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42888</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43995</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.43716</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5257200000000001</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.17752</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2981</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.06849</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5086499999999999</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.7708200000000001</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.23125</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.81153</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.54203</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.5247200000000001</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27479</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.36579</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.7624</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.93991</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.9167999999999999</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.44486</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.65444</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.79862</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.64186</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.00225</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.79015</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7447999999999999</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.68153</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.6095499999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.77646</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.59316</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.46017</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06788</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.66887</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43777</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33461</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5173300000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.38334</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.53588</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.41929</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43783</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45453</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37065</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39641</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4544</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4856</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.50662</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47974</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41082</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.51864</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.49163</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.17055</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.28738</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.40105</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.43537</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.9182100000000001</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5185700000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.6591</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5743200000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.64824</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.7483300000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.57589</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.50678</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5395399999999999</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.43093</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.4773</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.46311</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4083</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.37057</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34237</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.40565</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.43366</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.00341</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.86787</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45352</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37683</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.10707</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.17747</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.18913</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.23421</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.07293999999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.12974</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.23864</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.25152</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.28898</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2381</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.20285</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26678</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.12289</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.79691</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.2706</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33831</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.44151</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.66331</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47111</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43167</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36413</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29983</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28975</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.28974</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.28966</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30571</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.25925</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.05112</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.0518</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.05341</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04185</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04332</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03596</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04703</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.0455</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04823</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04586999999999999</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04764</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04192</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04447</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21825</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04054</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0464</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05521</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04751</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00378</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.01888</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15869</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.05832</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.11524</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38764</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37674</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40956</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46734</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.3546</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39977</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41646</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35493</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35063</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.68029</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42226</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42214</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10256</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04379</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04695000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04531</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04617</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04613</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.09905</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00408</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04385</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04556</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04357</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0434</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04416</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04455</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04729</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04769</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14292</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29521</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29373</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26898</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33545</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31765</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3147799999999999</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28814</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2713</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27108</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17248</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17102</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14778</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15951</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15867</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23626</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21408</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22664</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28585</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29089</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28117</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27202</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45605</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41547</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30104</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1563</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50775</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7909299999999999</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62209</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810900000000001</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92055</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49468</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91564</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8663099999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29858</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89146</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63244</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19103</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87074</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5412</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33481</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03568</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5346799999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79422</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5295299999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77625</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78012</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87717</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8755599999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49618</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40384</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45343</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21095</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87902</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55113</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62578</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53932</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49886</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45635</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43789</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43357</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39023</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40325</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4002</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58565</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59568</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60176</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6626000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58241</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.88024</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63091</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87948</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.86202</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8659199999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.46793</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34367</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31221</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41205</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41439</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39108</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9185399999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4645899999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35442</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.4646</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49897</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16644</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30869</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33074</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26271</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19351</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27853</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31259</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.28928</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2557</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.27805</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38538</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44768</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59493</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88995</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.33094</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.1384</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69824</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78851</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64444</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5776</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43946</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43669</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42282</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49917</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.4121</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42702</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44925</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39597</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43309</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39948</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49406</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.13235</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6303500000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.88258</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.84902</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25047</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.17357</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.69941</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.42993</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.78098</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.89923</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.34382</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.00814</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39997</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35215</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5776699999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46186</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.74954</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46387</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38526</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32344</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42129</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.10751</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.17165</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.79295</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.17855</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1.22707</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>1.19432</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15095</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.16093</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.15115</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.15974</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28363</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.24957</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.15947</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16104</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.16622</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38446</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39876</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44035</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4376</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44342</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34839</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53659</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46702</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42248</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.4146</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36958</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37924</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27104</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.2029</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.24967</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24275</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26946</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28781</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28927</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27773</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24146</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.30594</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24272</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35755</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36903</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3598</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36532</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45194</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.52189</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44162</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.72787</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.46046</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.29499</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24958</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.67453</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.12562</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.43558</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44886</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42628</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7077100000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.53227</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.25759</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30903</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.28442</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34465</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28092</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31779</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34941</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33606</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34575</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4112</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6526000000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7728400000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45103</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45738</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34375</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36176</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35567</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.20128</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28122</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.22381</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.27889</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28602</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30668</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.86812</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.7796900000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7730900000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.55414</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.77854</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.76575</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64735</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60565</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.58512</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46528</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.67167</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.46402</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.82496</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>1.0257</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40787</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47641</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35976</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48949</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5381699999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49401</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40726</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41548</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39821</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39426</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.40958</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40792</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41567</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39888</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41139</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44894</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.55747</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.4987</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44929</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45016</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.47426</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41955</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.69636</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.46704</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.30468</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6547200000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.25507</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33515</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.42092</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44137</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49361</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43984</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.5103799999999999</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51073</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54515</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.69599</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.72887</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.4044700000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.67041</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.81172</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59229</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5241699999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8315900000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7716000000000001</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6281</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6751900000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45006</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.48022</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48209</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46819</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55647</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43372</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45367</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39561</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3593</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39361</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.21046</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45064</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46168</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3295</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11843</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.1802</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29415</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>1.22264</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.44076</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40828</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.3958</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36471</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44414</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39828</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33756</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34395</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22621</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23086</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.29052</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25063</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26815</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13922</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25393</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.17174</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.1837</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22934</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23282</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28377</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35479</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33081</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38364</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38168</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.34939</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31302</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30635</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30316</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.30818</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.25134</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23683</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16293</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.20142</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.24901</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01848</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00119</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.03087</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04885</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11419</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01904</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03883</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00838</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.03379</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.02939</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04661999999999999</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02257</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.01899</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.19031</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04865999999999999</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04895</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04872</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04891</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03382</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04851</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.18279</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28061</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26121</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26286</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25916</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26636</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28058</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28727</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4109</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.28664</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.12331</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5631799999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.14445</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28405</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.27467</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25278</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.22833</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.25717</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24701</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21136</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23694</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.23966</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.27499</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26178</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.26155</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27177</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.27359</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.21793</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.14163</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62767</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60337</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.64389</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.5786100000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.1566</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11736</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.23525</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.17683</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.10576</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.06686</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.22538</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.09841</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.30923</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.02908</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.08853</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.16832</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02768</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.10714</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.11764</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.13699</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.02273</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.08921</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.10292</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.10116</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.14118</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33256</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36067</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.39229</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.46652</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36475</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36939</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.323</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33504</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33283</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.5732999999999999</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5577300000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.42194</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.43738</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48028</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27983</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36109</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36227</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.30462</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50384</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32832</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2785899999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.62874</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36835</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26425</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4961</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.50632</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48937</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.61954</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.44758</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.49762</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.38864</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45556</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.16839</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36763</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.48182</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40371</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37813</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3977</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.42023</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.42723</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.47263</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.36783</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3626</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.41508</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.5735</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.43501</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.52922</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.47634</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.43976</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.51554</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5835399999999999</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38622</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.42332</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.52655</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51059</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5530700000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.47249</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5181399999999999</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.70287</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87038</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.5847899999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.58412</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44217</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39851</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3742799999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37707</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37241</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.25704</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30888</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30948</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.22768</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.18124</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.16188</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.07576999999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.44488</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.22867</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.22041</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01183</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.17268</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.06593</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.06062</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.08064</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.17717</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08777</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.17966</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.16205</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.24746</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35724</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41579</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.42512</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35928</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.86521</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47025</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38474</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.25607</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24884</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11431</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.23848</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.25617</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.72296</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00389</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0487</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.02038</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.02588</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.24074</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.34618</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04852</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.23811</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.11284</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28628</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33559</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49889</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.43324</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.58129</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35917</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.61611</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39094</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28007</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.25767</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23003</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14385</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.20558</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.22917</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.23091</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1141</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15005</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.0018</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.0466</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04737</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04696</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.0418</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.07845000000000001</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03009</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09667000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17003</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.19556</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12031</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25424</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12388</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.05538000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26217</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.14607</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.11722</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.23639</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.18469</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23594</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.24287</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.24363</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3777</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36232</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39585</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46726</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38573</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38156</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3658</v>
       </c>
     </row>
   </sheetData>
